--- a/SGC-CKN/Excel/1f2c55b8-373e-40d2-96be-133742947cf4_Lô_CT-02_1-20_D800_22-03-2026.xlsx
+++ b/SGC-CKN/Excel/1f2c55b8-373e-40d2-96be-133742947cf4_Lô_CT-02_1-20_D800_22-03-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>1-20</t>
+    <t>P1-170</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>
